--- a/tests/corpus/xlsx/conditional.xlsx
+++ b/tests/corpus/xlsx/conditional.xlsx
@@ -613,8 +613,8 @@
         <color rgb="FF638EC6"/>
       </dataBar>
       <extLst>
-        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{87C45FDB-1BFD-4746-8D0C-7AE1E23C8C4D}</x14:id>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{00000000-0000-4000-8000-000000000001}">
+          <x14:id>{00000000-0000-4000-8000-000000000001}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -641,10 +641,10 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
   <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{00000000-0000-4000-8000-000000000001}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{87C45FDB-1BFD-4746-8D0C-7AE1E23C8C4D}">
+          <x14:cfRule type="dataBar" id="{00000000-0000-4000-8000-000000000001}">
             <x14:dataBar minLength="0" maxLength="100">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
